--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,117 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124084033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tujaskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>621430</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6346119</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1733,6 +1733,112 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129157262</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90949</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Thujaresevatet, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>621399</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6346160</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blandfskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90949</v>
+        <v>90952</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>90959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90959</v>
+        <v>90966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90969</v>
+        <v>90972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90972</v>
+        <v>90974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90974</v>
+        <v>90978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90978</v>
+        <v>90979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90979</v>
+        <v>90982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>129157262</v>
       </c>
       <c r="B11" t="n">
-        <v>90982</v>
+        <v>91010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31837-2021 artfynd.xlsx
+++ b/artfynd/A 31837-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6896697</v>
+        <v>84712</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tujabeståndet ost Skäftekärr, Öl</t>
+          <t>Skäftekärr, Tujabeståndet, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621389.7611653709</v>
+        <v>621378</v>
       </c>
       <c r="R2" t="n">
-        <v>6346126.168730629</v>
+        <v>6346122</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +747,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-Hö-Bor-0197</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +774,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>6896696</v>
       </c>
       <c r="B3" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621389.7611653709</v>
+        <v>621390</v>
       </c>
       <c r="R3" t="n">
-        <v>6346126.168730629</v>
+        <v>6346126</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +867,9 @@
           <t>2013-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +889,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80162080</v>
+        <v>67860328</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,49 +911,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>skätfekärr, Öl</t>
+          <t>Tujabeståndet, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621445.1707389976</v>
+        <v>621419</v>
       </c>
       <c r="R4" t="n">
-        <v>6346178.69938871</v>
+        <v>6346102</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,72 +979,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ola Elleström</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ola Elleström, Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95630748</v>
+        <v>67860327</v>
       </c>
       <c r="B5" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4191</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Thujaskogen, Öl</t>
+          <t>Tujabeståndet, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621419.8280139252</v>
+        <v>621419</v>
       </c>
       <c r="R5" t="n">
-        <v>6346118.394084386</v>
+        <v>6346102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,34 +1080,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tord Sundquist</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tord Sundquist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Leif Andersson, Rolf-Göran Carlsson, Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96428529</v>
+        <v>95630748</v>
       </c>
       <c r="B6" t="n">
-        <v>88852</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,27 +1130,23 @@
           <t>Berk. &amp; Broome</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Thujaskogen, Böda , Öl</t>
+          <t>Thujaskogen, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621420.288768507</v>
+        <v>621420</v>
       </c>
       <c r="R6" t="n">
-        <v>6346139.523281115</v>
+        <v>6346118</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,22 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,27 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Carlsson</t>
+          <t>Tord Sundquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Carlsson</t>
+          <t>Tord Sundquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111160772</v>
+        <v>96428529</v>
       </c>
       <c r="B7" t="n">
-        <v>96326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,42 +1214,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>4191</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Thujaskogen, Böda , Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621394.542237384</v>
+        <v>621420</v>
       </c>
       <c r="R7" t="n">
-        <v>6346147.96690535</v>
+        <v>6346140</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,33 +1289,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Björn Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111160185</v>
+        <v>120704674</v>
       </c>
       <c r="B8" t="n">
-        <v>108219</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,38 +1319,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>4191</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftekärr, Öl</t>
+          <t>Tujaskogen, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621406.4985915347</v>
+        <v>621396</v>
       </c>
       <c r="R8" t="n">
-        <v>6346147.237239314</v>
+        <v>6346124</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,22 +1380,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lång rad med jordstjärnor strax intill stigen nära parkeringen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,33 +1409,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Annika Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Annika Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120704674</v>
+        <v>129157262</v>
       </c>
       <c r="B9" t="n">
-        <v>90113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,24 +1456,20 @@
           <t>Berk. &amp; Broome</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tujaskogen, Öl</t>
+          <t>Thujaresevatet, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621396</v>
+        <v>621399</v>
       </c>
       <c r="R9" t="n">
-        <v>6346124</v>
+        <v>6346160</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,27 +1496,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lång rad med jordstjärnor strax intill stigen nära parkeringen.</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,76 +1514,69 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>blandfskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Olsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Olsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124084033</v>
+        <v>111160185</v>
       </c>
       <c r="B10" t="n">
-        <v>98123</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tujaskogen, Öl</t>
+          <t>Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621430</v>
+        <v>621406</v>
       </c>
       <c r="R10" t="n">
-        <v>6346119</v>
+        <v>6346147</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,12 +1600,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,29 +1624,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129157262</v>
+        <v>6896675</v>
       </c>
       <c r="B11" t="n">
-        <v>91010</v>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,37 +1653,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4191</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Thujaresevatet, Öl</t>
+          <t>Tujabeståndet ost Skäftekärr, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621399</v>
+        <v>621458</v>
       </c>
       <c r="R11" t="n">
-        <v>6346160</v>
+        <v>6346179</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,12 +1712,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2013-08-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,14 +1726,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>blandfskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1834,10 +1737,664 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>67543405</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Böda, Skäftekärr., Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621418</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6346089</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-08-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-08-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Skogskant</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>80162080</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>skätfekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621445</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6346179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ola Elleström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ola Elleström, Erling Jirle</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111160772</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621395</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6346148</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124084033</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tujaskogen, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>621430</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6346119</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129157270</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Thujaresevatet, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621448</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6346135</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>blandfskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6896697</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tujabeståndet ost Skäftekärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621390</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6346126</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2013-08-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2013-08-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
